--- a/diseases/d017/1995-1999.xlsx
+++ b/diseases/d017/1995-1999.xlsx
@@ -1803,7 +1803,7 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN7" t="b">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN11" t="b">
@@ -3403,7 +3403,7 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN15" t="b">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN19" t="b">
@@ -5003,7 +5003,7 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN23" t="b">
@@ -5803,7 +5803,7 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN27" t="b">
@@ -6603,7 +6603,7 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN31" t="b">
@@ -7403,7 +7403,7 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN35" t="b">
@@ -8203,7 +8203,7 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN39" t="b">
@@ -9003,7 +9003,7 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN43" t="b">
@@ -9803,7 +9803,7 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN47" t="b">
@@ -10603,7 +10603,7 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN51" t="b">
@@ -11793,7 +11793,7 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN57" t="b">
@@ -12593,7 +12593,7 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN61" t="b">
@@ -13393,7 +13393,7 @@
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN65" t="b">
@@ -14193,7 +14193,7 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN69" t="b">
@@ -14993,7 +14993,7 @@
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN73" t="b">
@@ -15793,7 +15793,7 @@
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN77" t="b">
@@ -16593,7 +16593,7 @@
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN81" t="b">
@@ -17393,7 +17393,7 @@
       </c>
       <c r="AM85" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN85" t="b">
@@ -18193,7 +18193,7 @@
       </c>
       <c r="AM89" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN89" t="b">
@@ -18993,7 +18993,7 @@
       </c>
       <c r="AM93" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN93" t="b">
@@ -19793,7 +19793,7 @@
       </c>
       <c r="AM97" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN97" t="b">
@@ -20593,7 +20593,7 @@
       </c>
       <c r="AM101" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN101" t="b">
@@ -22403,7 +22403,7 @@
       </c>
       <c r="AM110" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN110" t="b">
@@ -23584,7 +23584,7 @@
       </c>
       <c r="AM116" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN116" t="b">
@@ -24765,7 +24765,7 @@
       </c>
       <c r="AM122" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN122" t="b">
@@ -25946,7 +25946,7 @@
       </c>
       <c r="AM128" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN128" t="b">
@@ -27127,7 +27127,7 @@
       </c>
       <c r="AM134" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN134" t="b">
@@ -28308,7 +28308,7 @@
       </c>
       <c r="AM140" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN140" t="b">
@@ -29489,7 +29489,7 @@
       </c>
       <c r="AM146" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN146" t="b">
@@ -30670,7 +30670,7 @@
       </c>
       <c r="AM152" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN152" t="b">
@@ -31851,7 +31851,7 @@
       </c>
       <c r="AM158" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN158" t="b">
@@ -33032,7 +33032,7 @@
       </c>
       <c r="AM164" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN164" t="b">
@@ -34213,7 +34213,7 @@
       </c>
       <c r="AM170" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN170" t="b">
@@ -35394,7 +35394,7 @@
       </c>
       <c r="AM176" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN176" t="b">
@@ -37204,7 +37204,7 @@
       </c>
       <c r="AM185" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN185" t="b">
@@ -38385,7 +38385,7 @@
       </c>
       <c r="AM191" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN191" t="b">
@@ -39566,7 +39566,7 @@
       </c>
       <c r="AM197" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN197" t="b">
@@ -40747,7 +40747,7 @@
       </c>
       <c r="AM203" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN203" t="b">
@@ -41928,7 +41928,7 @@
       </c>
       <c r="AM209" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN209" t="b">
@@ -43109,7 +43109,7 @@
       </c>
       <c r="AM215" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN215" t="b">
@@ -44290,7 +44290,7 @@
       </c>
       <c r="AM221" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN221" t="b">
@@ -45471,7 +45471,7 @@
       </c>
       <c r="AM227" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN227" t="b">
@@ -46652,7 +46652,7 @@
       </c>
       <c r="AM233" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN233" t="b">
@@ -47833,7 +47833,7 @@
       </c>
       <c r="AM239" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN239" t="b">
@@ -49014,7 +49014,7 @@
       </c>
       <c r="AM245" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN245" t="b">
@@ -50195,7 +50195,7 @@
       </c>
       <c r="AM251" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN251" t="b">
@@ -61073,7 +61073,7 @@
       </c>
       <c r="AM306" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN306" t="b">
@@ -64443,7 +64443,7 @@
       </c>
       <c r="AM323" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN323" t="b">
@@ -65624,7 +65624,7 @@
       </c>
       <c r="AM329" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN329" t="b">
@@ -66805,7 +66805,7 @@
       </c>
       <c r="AM335" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN335" t="b">
@@ -67986,7 +67986,7 @@
       </c>
       <c r="AM341" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN341" t="b">
@@ -69167,7 +69167,7 @@
       </c>
       <c r="AM347" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN347" t="b">
@@ -70348,7 +70348,7 @@
       </c>
       <c r="AM353" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN353" t="b">
@@ -71529,7 +71529,7 @@
       </c>
       <c r="AM359" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN359" t="b">
@@ -72710,7 +72710,7 @@
       </c>
       <c r="AM365" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN365" t="b">
@@ -73891,7 +73891,7 @@
       </c>
       <c r="AM371" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN371" t="b">
@@ -75072,7 +75072,7 @@
       </c>
       <c r="AM377" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN377" t="b">
@@ -76253,7 +76253,7 @@
       </c>
       <c r="AM383" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN383" t="b">

--- a/diseases/d017/1995-1999.xlsx
+++ b/diseases/d017/1995-1999.xlsx
@@ -1803,7 +1803,7 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN7" t="b">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN11" t="b">
@@ -3403,7 +3403,7 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN15" t="b">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN19" t="b">
@@ -5003,7 +5003,7 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN23" t="b">
@@ -5803,7 +5803,7 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN27" t="b">
@@ -6603,7 +6603,7 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN31" t="b">
@@ -7403,7 +7403,7 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN35" t="b">
@@ -8203,7 +8203,7 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN39" t="b">
@@ -9003,7 +9003,7 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN43" t="b">
@@ -9803,7 +9803,7 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN47" t="b">
@@ -10603,7 +10603,7 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN51" t="b">
@@ -11793,7 +11793,7 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN57" t="b">
@@ -12593,7 +12593,7 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN61" t="b">
@@ -13393,7 +13393,7 @@
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN65" t="b">
@@ -14193,7 +14193,7 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN69" t="b">
@@ -14993,7 +14993,7 @@
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN73" t="b">
@@ -15793,7 +15793,7 @@
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN77" t="b">
@@ -16593,7 +16593,7 @@
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN81" t="b">
@@ -17393,7 +17393,7 @@
       </c>
       <c r="AM85" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN85" t="b">
@@ -18193,7 +18193,7 @@
       </c>
       <c r="AM89" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN89" t="b">
@@ -18993,7 +18993,7 @@
       </c>
       <c r="AM93" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN93" t="b">
@@ -19793,7 +19793,7 @@
       </c>
       <c r="AM97" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN97" t="b">
@@ -20593,7 +20593,7 @@
       </c>
       <c r="AM101" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN101" t="b">
@@ -21543,6 +21543,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO106" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22403,7 +22408,7 @@
       </c>
       <c r="AM110" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN110" t="b">
@@ -22963,6 +22968,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO113" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23584,7 +23594,7 @@
       </c>
       <c r="AM116" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN116" t="b">
@@ -24144,6 +24154,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO119" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24765,7 +24780,7 @@
       </c>
       <c r="AM122" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN122" t="b">
@@ -25325,6 +25340,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO125" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25946,7 +25966,7 @@
       </c>
       <c r="AM128" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN128" t="b">
@@ -26506,6 +26526,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO131" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27127,7 +27152,7 @@
       </c>
       <c r="AM134" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN134" t="b">
@@ -27687,6 +27712,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO137" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28308,7 +28338,7 @@
       </c>
       <c r="AM140" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN140" t="b">
@@ -28868,6 +28898,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO143" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29489,7 +29524,7 @@
       </c>
       <c r="AM146" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN146" t="b">
@@ -30049,6 +30084,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO149" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30670,7 +30710,7 @@
       </c>
       <c r="AM152" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN152" t="b">
@@ -31230,6 +31270,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO155" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31851,7 +31896,7 @@
       </c>
       <c r="AM158" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN158" t="b">
@@ -32411,6 +32456,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA161" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO161" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33032,7 +33082,7 @@
       </c>
       <c r="AM164" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN164" t="b">
@@ -33592,6 +33642,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO167" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34213,7 +34268,7 @@
       </c>
       <c r="AM170" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN170" t="b">
@@ -34773,6 +34828,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA173" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO173" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35394,7 +35454,7 @@
       </c>
       <c r="AM176" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN176" t="b">
@@ -36344,6 +36404,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA181" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO181" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37204,7 +37269,7 @@
       </c>
       <c r="AM185" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN185" t="b">
@@ -37764,6 +37829,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA188" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO188" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38385,7 +38455,7 @@
       </c>
       <c r="AM191" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN191" t="b">
@@ -38945,6 +39015,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA194" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO194" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39566,7 +39641,7 @@
       </c>
       <c r="AM197" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN197" t="b">
@@ -40126,6 +40201,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA200" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO200" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40747,7 +40827,7 @@
       </c>
       <c r="AM203" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN203" t="b">
@@ -41307,6 +41387,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA206" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO206" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41928,7 +42013,7 @@
       </c>
       <c r="AM209" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN209" t="b">
@@ -42488,6 +42573,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA212" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO212" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43109,7 +43199,7 @@
       </c>
       <c r="AM215" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN215" t="b">
@@ -43669,6 +43759,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA218" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO218" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -44290,7 +44385,7 @@
       </c>
       <c r="AM221" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN221" t="b">
@@ -44850,6 +44945,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA224" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO224" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -45471,7 +45571,7 @@
       </c>
       <c r="AM227" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN227" t="b">
@@ -46031,6 +46131,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA230" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO230" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -46652,7 +46757,7 @@
       </c>
       <c r="AM233" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN233" t="b">
@@ -47212,6 +47317,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA236" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO236" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -47833,7 +47943,7 @@
       </c>
       <c r="AM239" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN239" t="b">
@@ -48393,6 +48503,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA242" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO242" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -49014,7 +49129,7 @@
       </c>
       <c r="AM245" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN245" t="b">
@@ -49574,6 +49689,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA248" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO248" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -50195,7 +50315,7 @@
       </c>
       <c r="AM251" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN251" t="b">
@@ -56064,6 +56184,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA281" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO281" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -61073,7 +61198,7 @@
       </c>
       <c r="AM306" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN306" t="b">
@@ -63822,6 +63947,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA320" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO320" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -64443,7 +64573,7 @@
       </c>
       <c r="AM323" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN323" t="b">
@@ -65003,6 +65133,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA326" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO326" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -65624,7 +65759,7 @@
       </c>
       <c r="AM329" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN329" t="b">
@@ -66184,6 +66319,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA332" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO332" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -66805,7 +66945,7 @@
       </c>
       <c r="AM335" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN335" t="b">
@@ -67365,6 +67505,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA338" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO338" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -67986,7 +68131,7 @@
       </c>
       <c r="AM341" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN341" t="b">
@@ -68546,6 +68691,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA344" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO344" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -69167,7 +69317,7 @@
       </c>
       <c r="AM347" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN347" t="b">
@@ -69727,6 +69877,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA350" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO350" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -70348,7 +70503,7 @@
       </c>
       <c r="AM353" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN353" t="b">
@@ -70908,6 +71063,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA356" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO356" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -71529,7 +71689,7 @@
       </c>
       <c r="AM359" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN359" t="b">
@@ -72089,6 +72249,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA362" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO362" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -72710,7 +72875,7 @@
       </c>
       <c r="AM365" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN365" t="b">
@@ -73270,6 +73435,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA368" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO368" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -73891,7 +74061,7 @@
       </c>
       <c r="AM371" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN371" t="b">
@@ -74451,6 +74621,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA374" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO374" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -75072,7 +75247,7 @@
       </c>
       <c r="AM377" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN377" t="b">
@@ -75632,6 +75807,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA380" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO380" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -76253,7 +76433,7 @@
       </c>
       <c r="AM383" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN383" t="b">

--- a/diseases/d017/1995-1999.xlsx
+++ b/diseases/d017/1995-1999.xlsx
@@ -52843,7 +52843,7 @@
         </is>
       </c>
       <c r="AT264" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AU264" t="inlineStr">
         <is>
@@ -53077,7 +53077,7 @@
         </is>
       </c>
       <c r="AT265" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AU265" t="inlineStr">
         <is>

--- a/diseases/d017/1995-1999.xlsx
+++ b/diseases/d017/1995-1999.xlsx
@@ -23292,11 +23292,6 @@
       <c r="O159" t="n">
         <v>0</v>
       </c>
-      <c r="S159" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="U159" t="inlineStr">
         <is>
           <t>SER_SI_ECDC_MEAS_ANNUAL</t>
@@ -23314,12 +23309,7 @@
       </c>
       <c r="AP159" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ159" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS159" t="inlineStr">
@@ -23329,11 +23319,6 @@
       </c>
       <c r="AT159" t="n">
         <v>1</v>
-      </c>
-      <c r="AU159" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
       </c>
       <c r="AV159" t="inlineStr">
         <is>
@@ -23399,17 +23384,17 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Slovenia</t>
+          <t>Slovakia</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -23450,32 +23435,7 @@
       </c>
       <c r="U160" t="inlineStr">
         <is>
-          <t>SER_SI_ECDC_MEAS_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V160" t="inlineStr">
-        <is>
-          <t>SER_SI_ECDC_MEAS_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W160" t="inlineStr">
-        <is>
-          <t>SRC_SI_ECDC_ATLAS</t>
-        </is>
-      </c>
-      <c r="X160" t="inlineStr">
-        <is>
-          <t>Measles</t>
-        </is>
-      </c>
-      <c r="Y160" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z160" t="inlineStr">
-        <is>
-          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+          <t>SER_SK_ECDC_MEAS_ANNUAL</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
@@ -23483,64 +23443,6 @@
           <t>annual</t>
         </is>
       </c>
-      <c r="AB160" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC160" t="inlineStr">
-        <is>
-          <t>country:SI:national</t>
-        </is>
-      </c>
-      <c r="AD160" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE160" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF160" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG160" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH160" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI160" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ160" t="inlineStr">
-        <is>
-          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
-        </is>
-      </c>
-      <c r="AK160" t="inlineStr">
-        <is>
-          <t>Slovenia annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
-        </is>
-      </c>
-      <c r="AM160" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN160" t="b">
-        <v>1</v>
-      </c>
       <c r="AO160" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -23548,27 +23450,17 @@
       </c>
       <c r="AP160" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ160" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS160" t="inlineStr">
         <is>
-          <t>SER_SI_ECDC_MEAS_ANNUAL</t>
+          <t>SER_SK_ECDC_MEAS_ANNUAL</t>
         </is>
       </c>
       <c r="AT160" t="n">
         <v>1</v>
       </c>
-      <c r="AU160" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
       <c r="AV160" t="inlineStr">
         <is>
           <t>ecdc_atlas_annual</t>
@@ -23576,7 +23468,7 @@
       </c>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Slovakia Annual Baseline</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
@@ -23596,7 +23488,7 @@
       </c>
       <c r="BA160" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Slovakia Annual Baseline</t>
         </is>
       </c>
       <c r="BB160" t="inlineStr">
@@ -23638,12 +23530,12 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Slovakia</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -23668,12 +23560,12 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>1999-01-01</t>
+          <t>1999-02-01</t>
         </is>
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>1999-01</t>
+          <t>1999-02</t>
         </is>
       </c>
       <c r="N161" t="n">
@@ -23684,12 +23576,12 @@
       </c>
       <c r="U161" t="inlineStr">
         <is>
-          <t>SER_SK_ECDC_MEAS_ANNUAL</t>
+          <t>SER_FI_THL_TTR_170</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
         <is>
-          <t>annual</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO161" t="inlineStr">
@@ -23704,7 +23596,7 @@
       </c>
       <c r="AS161" t="inlineStr">
         <is>
-          <t>SER_SK_ECDC_MEAS_ANNUAL</t>
+          <t>SER_FI_THL_TTR_170</t>
         </is>
       </c>
       <c r="AT161" t="n">
@@ -23712,42 +23604,42 @@
       </c>
       <c r="AV161" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Slovakia Annual Baseline</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ161" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA161" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Slovakia Annual Baseline</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB161" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC161" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -23779,12 +23671,12 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -23818,15 +23710,13 @@
         </is>
       </c>
       <c r="N162" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O162" t="n">
-        <v>0</v>
-      </c>
-      <c r="U162" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_170</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="Q162" t="n">
+        <v>0</v>
       </c>
       <c r="AA162" t="inlineStr">
         <is>
@@ -23835,7 +23725,7 @@
       </c>
       <c r="AO162" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP162" t="inlineStr">
@@ -23843,52 +23733,48 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS162" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_170</t>
-        </is>
-      </c>
+      <c r="AS162" t="inlineStr"/>
       <c r="AT162" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV162" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ162" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA162" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB162" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC162" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -23920,12 +23806,12 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -23959,13 +23845,15 @@
         </is>
       </c>
       <c r="N163" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O163" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q163" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="U163" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_107_MONTHLY</t>
+        </is>
       </c>
       <c r="AA163" t="inlineStr">
         <is>
@@ -23974,7 +23862,7 @@
       </c>
       <c r="AO163" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP163" t="inlineStr">
@@ -23982,48 +23870,52 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS163" t="inlineStr"/>
+      <c r="AS163" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_107_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT163" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV163" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ163" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA163" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB163" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC163" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -24055,12 +23947,12 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -24085,12 +23977,12 @@
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>1999-02-01</t>
+          <t>1999-03-01</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>1999-02</t>
+          <t>1999-03</t>
         </is>
       </c>
       <c r="N164" t="n">
@@ -24101,7 +23993,7 @@
       </c>
       <c r="U164" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_107_MONTHLY</t>
+          <t>SER_FI_THL_TTR_170</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
@@ -24121,7 +24013,7 @@
       </c>
       <c r="AS164" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_107_MONTHLY</t>
+          <t>SER_FI_THL_TTR_170</t>
         </is>
       </c>
       <c r="AT164" t="n">
@@ -24129,42 +24021,42 @@
       </c>
       <c r="AV164" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ164" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA164" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB164" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC164" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -24196,12 +24088,12 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -24235,15 +24127,13 @@
         </is>
       </c>
       <c r="N165" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O165" t="n">
-        <v>0</v>
-      </c>
-      <c r="U165" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_170</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="Q165" t="n">
+        <v>0</v>
       </c>
       <c r="AA165" t="inlineStr">
         <is>
@@ -24252,7 +24142,7 @@
       </c>
       <c r="AO165" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP165" t="inlineStr">
@@ -24260,52 +24150,48 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS165" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_170</t>
-        </is>
-      </c>
+      <c r="AS165" t="inlineStr"/>
       <c r="AT165" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV165" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ165" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA165" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB165" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC165" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -24337,12 +24223,12 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -24376,13 +24262,15 @@
         </is>
       </c>
       <c r="N166" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O166" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q166" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="U166" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_107_MONTHLY</t>
+        </is>
       </c>
       <c r="AA166" t="inlineStr">
         <is>
@@ -24391,7 +24279,7 @@
       </c>
       <c r="AO166" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP166" t="inlineStr">
@@ -24399,48 +24287,52 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS166" t="inlineStr"/>
+      <c r="AS166" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_107_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT166" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV166" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ166" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA166" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB166" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC166" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -24472,12 +24364,12 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -24502,12 +24394,12 @@
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>1999-03-01</t>
+          <t>1999-04-01</t>
         </is>
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>1999-03</t>
+          <t>1999-04</t>
         </is>
       </c>
       <c r="N167" t="n">
@@ -24518,7 +24410,7 @@
       </c>
       <c r="U167" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_107_MONTHLY</t>
+          <t>SER_FI_THL_TTR_170</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
@@ -24538,7 +24430,7 @@
       </c>
       <c r="AS167" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_107_MONTHLY</t>
+          <t>SER_FI_THL_TTR_170</t>
         </is>
       </c>
       <c r="AT167" t="n">
@@ -24546,42 +24438,42 @@
       </c>
       <c r="AV167" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ167" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA167" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB167" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC167" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -24613,12 +24505,12 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -24652,15 +24544,13 @@
         </is>
       </c>
       <c r="N168" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O168" t="n">
-        <v>0</v>
-      </c>
-      <c r="U168" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_170</t>
-        </is>
+        <v>6</v>
+      </c>
+      <c r="Q168" t="n">
+        <v>0</v>
       </c>
       <c r="AA168" t="inlineStr">
         <is>
@@ -24669,7 +24559,7 @@
       </c>
       <c r="AO168" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP168" t="inlineStr">
@@ -24677,52 +24567,48 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS168" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_170</t>
-        </is>
-      </c>
+      <c r="AS168" t="inlineStr"/>
       <c r="AT168" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV168" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ168" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA168" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB168" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC168" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -24754,12 +24640,12 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -24793,13 +24679,15 @@
         </is>
       </c>
       <c r="N169" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O169" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q169" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="U169" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_107_MONTHLY</t>
+        </is>
       </c>
       <c r="AA169" t="inlineStr">
         <is>
@@ -24808,7 +24696,7 @@
       </c>
       <c r="AO169" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP169" t="inlineStr">
@@ -24816,48 +24704,52 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS169" t="inlineStr"/>
+      <c r="AS169" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_107_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT169" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV169" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ169" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA169" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB169" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC169" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -24889,12 +24781,12 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -24919,12 +24811,12 @@
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>1999-04-01</t>
+          <t>1999-05-01</t>
         </is>
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>1999-04</t>
+          <t>1999-05</t>
         </is>
       </c>
       <c r="N170" t="n">
@@ -24935,7 +24827,7 @@
       </c>
       <c r="U170" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_107_MONTHLY</t>
+          <t>SER_FI_THL_TTR_170</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
@@ -24955,7 +24847,7 @@
       </c>
       <c r="AS170" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_107_MONTHLY</t>
+          <t>SER_FI_THL_TTR_170</t>
         </is>
       </c>
       <c r="AT170" t="n">
@@ -24963,42 +24855,42 @@
       </c>
       <c r="AV170" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ170" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA170" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB170" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC170" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -25030,12 +24922,12 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -25069,15 +24961,13 @@
         </is>
       </c>
       <c r="N171" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O171" t="n">
-        <v>0</v>
-      </c>
-      <c r="U171" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_170</t>
-        </is>
+        <v>8</v>
+      </c>
+      <c r="Q171" t="n">
+        <v>0</v>
       </c>
       <c r="AA171" t="inlineStr">
         <is>
@@ -25086,7 +24976,7 @@
       </c>
       <c r="AO171" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP171" t="inlineStr">
@@ -25094,52 +24984,48 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS171" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_170</t>
-        </is>
-      </c>
+      <c r="AS171" t="inlineStr"/>
       <c r="AT171" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV171" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ171" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA171" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB171" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC171" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -25171,12 +25057,12 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -25210,13 +25096,15 @@
         </is>
       </c>
       <c r="N172" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O172" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q172" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="U172" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_107_MONTHLY</t>
+        </is>
       </c>
       <c r="AA172" t="inlineStr">
         <is>
@@ -25225,7 +25113,7 @@
       </c>
       <c r="AO172" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP172" t="inlineStr">
@@ -25233,48 +25121,52 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS172" t="inlineStr"/>
+      <c r="AS172" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_107_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT172" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV172" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ172" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA172" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB172" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC172" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -25306,12 +25198,12 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -25336,12 +25228,12 @@
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>1999-05-01</t>
+          <t>1999-06-01</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>1999-05</t>
+          <t>1999-06</t>
         </is>
       </c>
       <c r="N173" t="n">
@@ -25352,7 +25244,7 @@
       </c>
       <c r="U173" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_107_MONTHLY</t>
+          <t>SER_FI_THL_TTR_170</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
@@ -25372,7 +25264,7 @@
       </c>
       <c r="AS173" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_107_MONTHLY</t>
+          <t>SER_FI_THL_TTR_170</t>
         </is>
       </c>
       <c r="AT173" t="n">
@@ -25380,42 +25272,42 @@
       </c>
       <c r="AV173" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ173" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA173" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB173" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC173" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -25447,12 +25339,12 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -25491,10 +25383,8 @@
       <c r="O174" t="n">
         <v>0</v>
       </c>
-      <c r="U174" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_170</t>
-        </is>
+      <c r="Q174" t="n">
+        <v>0</v>
       </c>
       <c r="AA174" t="inlineStr">
         <is>
@@ -25503,7 +25393,7 @@
       </c>
       <c r="AO174" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP174" t="inlineStr">
@@ -25511,52 +25401,48 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS174" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_170</t>
-        </is>
-      </c>
+      <c r="AS174" t="inlineStr"/>
       <c r="AT174" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV174" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ174" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA174" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB174" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC174" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -25588,12 +25474,12 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -25632,8 +25518,10 @@
       <c r="O175" t="n">
         <v>0</v>
       </c>
-      <c r="Q175" t="n">
-        <v>0</v>
+      <c r="U175" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_107_MONTHLY</t>
+        </is>
       </c>
       <c r="AA175" t="inlineStr">
         <is>
@@ -25642,7 +25530,7 @@
       </c>
       <c r="AO175" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP175" t="inlineStr">
@@ -25650,48 +25538,52 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS175" t="inlineStr"/>
+      <c r="AS175" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_107_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT175" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV175" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ175" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA175" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB175" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC175" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -25723,12 +25615,12 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -25753,12 +25645,12 @@
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>1999-06-01</t>
+          <t>1999-07-01</t>
         </is>
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>1999-06</t>
+          <t>1999-07</t>
         </is>
       </c>
       <c r="N176" t="n">
@@ -25769,7 +25661,7 @@
       </c>
       <c r="U176" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_107_MONTHLY</t>
+          <t>SER_FI_THL_TTR_170</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
@@ -25789,7 +25681,7 @@
       </c>
       <c r="AS176" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_107_MONTHLY</t>
+          <t>SER_FI_THL_TTR_170</t>
         </is>
       </c>
       <c r="AT176" t="n">
@@ -25797,42 +25689,42 @@
       </c>
       <c r="AV176" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ176" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA176" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB176" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC176" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -25864,12 +25756,12 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -25903,15 +25795,13 @@
         </is>
       </c>
       <c r="N177" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O177" t="n">
-        <v>0</v>
-      </c>
-      <c r="U177" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_170</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="Q177" t="n">
+        <v>0</v>
       </c>
       <c r="AA177" t="inlineStr">
         <is>
@@ -25920,7 +25810,7 @@
       </c>
       <c r="AO177" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP177" t="inlineStr">
@@ -25928,52 +25818,48 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS177" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_170</t>
-        </is>
-      </c>
+      <c r="AS177" t="inlineStr"/>
       <c r="AT177" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV177" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW177" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ177" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA177" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB177" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC177" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -26005,12 +25891,12 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -26044,13 +25930,15 @@
         </is>
       </c>
       <c r="N178" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O178" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q178" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="U178" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_107_MONTHLY</t>
+        </is>
       </c>
       <c r="AA178" t="inlineStr">
         <is>
@@ -26059,7 +25947,7 @@
       </c>
       <c r="AO178" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP178" t="inlineStr">
@@ -26067,48 +25955,52 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS178" t="inlineStr"/>
+      <c r="AS178" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_107_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT178" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV178" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ178" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA178" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB178" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC178" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -26140,12 +26032,12 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -26170,12 +26062,12 @@
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>1999-07-01</t>
+          <t>1999-08-01</t>
         </is>
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>1999-07</t>
+          <t>1999-08</t>
         </is>
       </c>
       <c r="N179" t="n">
@@ -26186,7 +26078,7 @@
       </c>
       <c r="U179" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_107_MONTHLY</t>
+          <t>SER_FI_THL_TTR_170</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
@@ -26206,7 +26098,7 @@
       </c>
       <c r="AS179" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_107_MONTHLY</t>
+          <t>SER_FI_THL_TTR_170</t>
         </is>
       </c>
       <c r="AT179" t="n">
@@ -26214,42 +26106,42 @@
       </c>
       <c r="AV179" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW179" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY179" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ179" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA179" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB179" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC179" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -26281,12 +26173,12 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -26320,15 +26212,13 @@
         </is>
       </c>
       <c r="N180" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O180" t="n">
-        <v>0</v>
-      </c>
-      <c r="U180" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_170</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="Q180" t="n">
+        <v>0</v>
       </c>
       <c r="AA180" t="inlineStr">
         <is>
@@ -26337,7 +26227,7 @@
       </c>
       <c r="AO180" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP180" t="inlineStr">
@@ -26345,52 +26235,48 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS180" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_170</t>
-        </is>
-      </c>
+      <c r="AS180" t="inlineStr"/>
       <c r="AT180" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV180" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW180" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ180" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA180" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB180" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC180" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -26422,12 +26308,12 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -26466,8 +26352,10 @@
       <c r="O181" t="n">
         <v>1</v>
       </c>
-      <c r="Q181" t="n">
-        <v>0</v>
+      <c r="U181" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_107_MONTHLY</t>
+        </is>
       </c>
       <c r="AA181" t="inlineStr">
         <is>
@@ -26476,7 +26364,7 @@
       </c>
       <c r="AO181" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP181" t="inlineStr">
@@ -26484,48 +26372,52 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS181" t="inlineStr"/>
+      <c r="AS181" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_107_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT181" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV181" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW181" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX181" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY181" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ181" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA181" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB181" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC181" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -26557,12 +26449,12 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -26587,23 +26479,23 @@
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>1999-08-01</t>
+          <t>1999-09-01</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>1999-08</t>
+          <t>1999-09</t>
         </is>
       </c>
       <c r="N182" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O182" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U182" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_107_MONTHLY</t>
+          <t>SER_FI_THL_TTR_170</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
@@ -26623,7 +26515,7 @@
       </c>
       <c r="AS182" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_107_MONTHLY</t>
+          <t>SER_FI_THL_TTR_170</t>
         </is>
       </c>
       <c r="AT182" t="n">
@@ -26631,42 +26523,42 @@
       </c>
       <c r="AV182" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW182" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ182" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA182" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB182" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC182" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -26698,12 +26590,12 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -26742,10 +26634,8 @@
       <c r="O183" t="n">
         <v>0</v>
       </c>
-      <c r="U183" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_170</t>
-        </is>
+      <c r="Q183" t="n">
+        <v>0</v>
       </c>
       <c r="AA183" t="inlineStr">
         <is>
@@ -26754,7 +26644,7 @@
       </c>
       <c r="AO183" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP183" t="inlineStr">
@@ -26762,52 +26652,48 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS183" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_170</t>
-        </is>
-      </c>
+      <c r="AS183" t="inlineStr"/>
       <c r="AT183" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV183" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW183" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ183" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA183" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB183" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC183" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -26839,12 +26725,12 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -26883,8 +26769,10 @@
       <c r="O184" t="n">
         <v>0</v>
       </c>
-      <c r="Q184" t="n">
-        <v>0</v>
+      <c r="U184" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_107_MONTHLY</t>
+        </is>
       </c>
       <c r="AA184" t="inlineStr">
         <is>
@@ -26893,7 +26781,7 @@
       </c>
       <c r="AO184" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP184" t="inlineStr">
@@ -26901,48 +26789,52 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS184" t="inlineStr"/>
+      <c r="AS184" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_107_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT184" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV184" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW184" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ184" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA184" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB184" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC184" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -26974,12 +26866,12 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -27004,12 +26896,12 @@
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>1999-09-01</t>
+          <t>1999-10-01</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>1999-09</t>
+          <t>1999-10</t>
         </is>
       </c>
       <c r="N185" t="n">
@@ -27020,7 +26912,7 @@
       </c>
       <c r="U185" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_107_MONTHLY</t>
+          <t>SER_FI_THL_TTR_170</t>
         </is>
       </c>
       <c r="AA185" t="inlineStr">
@@ -27040,7 +26932,7 @@
       </c>
       <c r="AS185" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_107_MONTHLY</t>
+          <t>SER_FI_THL_TTR_170</t>
         </is>
       </c>
       <c r="AT185" t="n">
@@ -27048,42 +26940,42 @@
       </c>
       <c r="AV185" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW185" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ185" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA185" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB185" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC185" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -27115,12 +27007,12 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -27154,15 +27046,13 @@
         </is>
       </c>
       <c r="N186" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O186" t="n">
-        <v>0</v>
-      </c>
-      <c r="U186" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_170</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="Q186" t="n">
+        <v>0</v>
       </c>
       <c r="AA186" t="inlineStr">
         <is>
@@ -27171,7 +27061,7 @@
       </c>
       <c r="AO186" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP186" t="inlineStr">
@@ -27179,52 +27069,48 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS186" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_170</t>
-        </is>
-      </c>
+      <c r="AS186" t="inlineStr"/>
       <c r="AT186" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV186" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ186" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA186" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB186" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC186" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -27256,12 +27142,12 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -27295,71 +27181,77 @@
         </is>
       </c>
       <c r="N187" t="n">
+        <v>0</v>
+      </c>
+      <c r="O187" t="n">
+        <v>0</v>
+      </c>
+      <c r="U187" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_107_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA187" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO187" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP187" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS187" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_107_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT187" t="n">
         <v>1</v>
       </c>
-      <c r="O187" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q187" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA187" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO187" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP187" t="inlineStr">
-        <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS187" t="inlineStr"/>
-      <c r="AT187" t="n">
-        <v>0</v>
-      </c>
       <c r="AV187" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ187" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA187" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB187" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC187" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -27391,12 +27283,12 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -27421,12 +27313,12 @@
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>1999-10-01</t>
+          <t>1999-11-01</t>
         </is>
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>1999-10</t>
+          <t>1999-11</t>
         </is>
       </c>
       <c r="N188" t="n">
@@ -27437,7 +27329,7 @@
       </c>
       <c r="U188" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_107_MONTHLY</t>
+          <t>SER_FI_THL_TTR_170</t>
         </is>
       </c>
       <c r="AA188" t="inlineStr">
@@ -27457,7 +27349,7 @@
       </c>
       <c r="AS188" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_107_MONTHLY</t>
+          <t>SER_FI_THL_TTR_170</t>
         </is>
       </c>
       <c r="AT188" t="n">
@@ -27465,42 +27357,42 @@
       </c>
       <c r="AV188" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ188" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA188" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB188" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC188" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -27532,12 +27424,12 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -27571,15 +27463,13 @@
         </is>
       </c>
       <c r="N189" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O189" t="n">
-        <v>0</v>
-      </c>
-      <c r="U189" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_170</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="Q189" t="n">
+        <v>0</v>
       </c>
       <c r="AA189" t="inlineStr">
         <is>
@@ -27588,7 +27478,7 @@
       </c>
       <c r="AO189" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP189" t="inlineStr">
@@ -27596,52 +27486,48 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS189" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_170</t>
-        </is>
-      </c>
+      <c r="AS189" t="inlineStr"/>
       <c r="AT189" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV189" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ189" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA189" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB189" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC189" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -27673,12 +27559,12 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -27717,8 +27603,10 @@
       <c r="O190" t="n">
         <v>1</v>
       </c>
-      <c r="Q190" t="n">
-        <v>0</v>
+      <c r="U190" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_107_MONTHLY</t>
+        </is>
       </c>
       <c r="AA190" t="inlineStr">
         <is>
@@ -27727,7 +27615,7 @@
       </c>
       <c r="AO190" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP190" t="inlineStr">
@@ -27735,48 +27623,52 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS190" t="inlineStr"/>
+      <c r="AS190" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_107_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT190" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV190" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ190" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA190" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB190" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC190" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -27808,12 +27700,12 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -27838,23 +27730,23 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>1999-11-01</t>
+          <t>1999-12-01</t>
         </is>
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>1999-11</t>
+          <t>1999-12</t>
         </is>
       </c>
       <c r="N191" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O191" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U191" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_107_MONTHLY</t>
+          <t>SER_FI_THL_TTR_170</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
@@ -27874,7 +27766,7 @@
       </c>
       <c r="AS191" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_107_MONTHLY</t>
+          <t>SER_FI_THL_TTR_170</t>
         </is>
       </c>
       <c r="AT191" t="n">
@@ -27882,42 +27774,42 @@
       </c>
       <c r="AV191" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ191" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA191" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB191" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC191" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -27949,12 +27841,12 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -27988,15 +27880,13 @@
         </is>
       </c>
       <c r="N192" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O192" t="n">
-        <v>0</v>
-      </c>
-      <c r="U192" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_170</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="Q192" t="n">
+        <v>0</v>
       </c>
       <c r="AA192" t="inlineStr">
         <is>
@@ -28005,7 +27895,7 @@
       </c>
       <c r="AO192" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP192" t="inlineStr">
@@ -28013,52 +27903,48 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS192" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_170</t>
-        </is>
-      </c>
+      <c r="AS192" t="inlineStr"/>
       <c r="AT192" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV192" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW192" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY192" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ192" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA192" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB192" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC192" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -28090,12 +27976,12 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -28129,13 +28015,15 @@
         </is>
       </c>
       <c r="N193" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O193" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q193" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="U193" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_107_MONTHLY</t>
+        </is>
       </c>
       <c r="AA193" t="inlineStr">
         <is>
@@ -28144,7 +28032,7 @@
       </c>
       <c r="AO193" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP193" t="inlineStr">
@@ -28152,187 +28040,50 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS193" t="inlineStr"/>
+      <c r="AS193" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_107_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT193" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV193" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ193" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA193" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB193" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC193" t="inlineStr">
-        <is>
-          <t>open_data_csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B194" t="inlineStr">
-        <is>
-          <t>D017</t>
-        </is>
-      </c>
-      <c r="C194" t="inlineStr">
-        <is>
-          <t>measles</t>
-        </is>
-      </c>
-      <c r="D194" t="inlineStr">
-        <is>
-          <t>Measles</t>
-        </is>
-      </c>
-      <c r="E194" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F194" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G194" t="inlineStr">
-        <is>
-          <t>Norway</t>
-        </is>
-      </c>
-      <c r="H194" t="inlineStr">
-        <is>
-          <t>D017</t>
-        </is>
-      </c>
-      <c r="I194" t="inlineStr">
-        <is>
-          <t>Measles</t>
-        </is>
-      </c>
-      <c r="J194" t="inlineStr">
-        <is>
-          <t>麻疹</t>
-        </is>
-      </c>
-      <c r="K194" t="inlineStr">
-        <is>
-          <t>Viral</t>
-        </is>
-      </c>
-      <c r="L194" t="inlineStr">
-        <is>
-          <t>1999-12-01</t>
-        </is>
-      </c>
-      <c r="M194" t="inlineStr">
-        <is>
-          <t>1999-12</t>
-        </is>
-      </c>
-      <c r="N194" t="n">
-        <v>1</v>
-      </c>
-      <c r="O194" t="n">
-        <v>1</v>
-      </c>
-      <c r="U194" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_107_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA194" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO194" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP194" t="inlineStr">
-        <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS194" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_107_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AT194" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV194" t="inlineStr">
-        <is>
-          <t>fhi_msis</t>
-        </is>
-      </c>
-      <c r="AW194" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
-        </is>
-      </c>
-      <c r="AX194" t="inlineStr">
-        <is>
-          <t>https://allvis.fhi.no/msis</t>
-        </is>
-      </c>
-      <c r="AY194" t="inlineStr">
-        <is>
-          <t>official_json_api</t>
-        </is>
-      </c>
-      <c r="AZ194" t="inlineStr">
-        <is>
-          <t>fhi_msis</t>
-        </is>
-      </c>
-      <c r="BA194" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
-        </is>
-      </c>
-      <c r="BB194" t="inlineStr">
-        <is>
-          <t>https://allvis.fhi.no/msis</t>
-        </is>
-      </c>
-      <c r="BC194" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -28464,7 +28215,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="11">
@@ -28484,7 +28235,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
@@ -28494,7 +28245,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">

--- a/diseases/d017/1995-1999.xlsx
+++ b/diseases/d017/1995-1999.xlsx
@@ -21538,6 +21538,11 @@
       <c r="Q106" t="n">
         <v>0</v>
       </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21550,13 +21555,23 @@
       </c>
       <c r="AP106" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR106" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS106" t="inlineStr"/>
       <c r="AT106" t="n">
         <v>0</v>
       </c>
+      <c r="AU106" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV106" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -22948,6 +22963,11 @@
       <c r="Q113" t="n">
         <v>0</v>
       </c>
+      <c r="S113" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA113" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -22960,13 +22980,23 @@
       </c>
       <c r="AP113" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR113" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS113" t="inlineStr"/>
       <c r="AT113" t="n">
         <v>0</v>
       </c>
+      <c r="AU113" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV113" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -24119,6 +24149,11 @@
       <c r="Q119" t="n">
         <v>0</v>
       </c>
+      <c r="S119" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA119" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -24131,13 +24166,23 @@
       </c>
       <c r="AP119" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR119" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS119" t="inlineStr"/>
       <c r="AT119" t="n">
         <v>0</v>
       </c>
+      <c r="AU119" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV119" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -25290,6 +25335,11 @@
       <c r="Q125" t="n">
         <v>0</v>
       </c>
+      <c r="S125" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA125" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -25302,13 +25352,23 @@
       </c>
       <c r="AP125" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR125" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS125" t="inlineStr"/>
       <c r="AT125" t="n">
         <v>0</v>
       </c>
+      <c r="AU125" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV125" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -26461,6 +26521,11 @@
       <c r="Q131" t="n">
         <v>0</v>
       </c>
+      <c r="S131" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA131" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -26473,13 +26538,23 @@
       </c>
       <c r="AP131" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR131" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS131" t="inlineStr"/>
       <c r="AT131" t="n">
         <v>0</v>
       </c>
+      <c r="AU131" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV131" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -27632,6 +27707,11 @@
       <c r="Q137" t="n">
         <v>0</v>
       </c>
+      <c r="S137" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA137" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -27644,13 +27724,23 @@
       </c>
       <c r="AP137" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR137" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS137" t="inlineStr"/>
       <c r="AT137" t="n">
         <v>0</v>
       </c>
+      <c r="AU137" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV137" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -28803,6 +28893,11 @@
       <c r="Q143" t="n">
         <v>0</v>
       </c>
+      <c r="S143" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA143" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -28815,13 +28910,23 @@
       </c>
       <c r="AP143" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR143" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS143" t="inlineStr"/>
       <c r="AT143" t="n">
         <v>0</v>
       </c>
+      <c r="AU143" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV143" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -29974,6 +30079,11 @@
       <c r="Q149" t="n">
         <v>0</v>
       </c>
+      <c r="S149" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA149" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -29986,13 +30096,23 @@
       </c>
       <c r="AP149" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR149" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS149" t="inlineStr"/>
       <c r="AT149" t="n">
         <v>0</v>
       </c>
+      <c r="AU149" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV149" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -31145,6 +31265,11 @@
       <c r="Q155" t="n">
         <v>0</v>
       </c>
+      <c r="S155" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA155" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -31157,13 +31282,23 @@
       </c>
       <c r="AP155" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR155" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS155" t="inlineStr"/>
       <c r="AT155" t="n">
         <v>0</v>
       </c>
+      <c r="AU155" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV155" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -32316,6 +32451,11 @@
       <c r="Q161" t="n">
         <v>0</v>
       </c>
+      <c r="S161" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA161" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -32328,13 +32468,23 @@
       </c>
       <c r="AP161" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR161" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS161" t="inlineStr"/>
       <c r="AT161" t="n">
         <v>0</v>
       </c>
+      <c r="AU161" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV161" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -33487,6 +33637,11 @@
       <c r="Q167" t="n">
         <v>0</v>
       </c>
+      <c r="S167" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA167" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -33499,13 +33654,23 @@
       </c>
       <c r="AP167" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR167" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS167" t="inlineStr"/>
       <c r="AT167" t="n">
         <v>0</v>
       </c>
+      <c r="AU167" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV167" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -34658,6 +34823,11 @@
       <c r="Q173" t="n">
         <v>0</v>
       </c>
+      <c r="S173" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA173" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -34670,13 +34840,23 @@
       </c>
       <c r="AP173" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR173" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS173" t="inlineStr"/>
       <c r="AT173" t="n">
         <v>0</v>
       </c>
+      <c r="AU173" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV173" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -36219,6 +36399,11 @@
       <c r="Q181" t="n">
         <v>0</v>
       </c>
+      <c r="S181" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA181" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -36231,13 +36416,23 @@
       </c>
       <c r="AP181" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR181" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS181" t="inlineStr"/>
       <c r="AT181" t="n">
         <v>0</v>
       </c>
+      <c r="AU181" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV181" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -37629,6 +37824,11 @@
       <c r="Q188" t="n">
         <v>0</v>
       </c>
+      <c r="S188" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA188" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -37641,13 +37841,23 @@
       </c>
       <c r="AP188" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR188" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS188" t="inlineStr"/>
       <c r="AT188" t="n">
         <v>0</v>
       </c>
+      <c r="AU188" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV188" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -38800,6 +39010,11 @@
       <c r="Q194" t="n">
         <v>0</v>
       </c>
+      <c r="S194" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA194" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -38812,13 +39027,23 @@
       </c>
       <c r="AP194" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR194" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS194" t="inlineStr"/>
       <c r="AT194" t="n">
         <v>0</v>
       </c>
+      <c r="AU194" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV194" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -39971,6 +40196,11 @@
       <c r="Q200" t="n">
         <v>0</v>
       </c>
+      <c r="S200" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA200" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -39983,13 +40213,23 @@
       </c>
       <c r="AP200" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR200" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS200" t="inlineStr"/>
       <c r="AT200" t="n">
         <v>0</v>
       </c>
+      <c r="AU200" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV200" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -41142,6 +41382,11 @@
       <c r="Q206" t="n">
         <v>0</v>
       </c>
+      <c r="S206" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA206" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -41154,13 +41399,23 @@
       </c>
       <c r="AP206" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR206" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS206" t="inlineStr"/>
       <c r="AT206" t="n">
         <v>0</v>
       </c>
+      <c r="AU206" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV206" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -42313,6 +42568,11 @@
       <c r="Q212" t="n">
         <v>0</v>
       </c>
+      <c r="S212" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA212" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -42325,13 +42585,23 @@
       </c>
       <c r="AP212" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR212" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS212" t="inlineStr"/>
       <c r="AT212" t="n">
         <v>0</v>
       </c>
+      <c r="AU212" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV212" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -43484,6 +43754,11 @@
       <c r="Q218" t="n">
         <v>0</v>
       </c>
+      <c r="S218" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA218" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -43496,13 +43771,23 @@
       </c>
       <c r="AP218" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR218" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS218" t="inlineStr"/>
       <c r="AT218" t="n">
         <v>0</v>
       </c>
+      <c r="AU218" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV218" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -44655,6 +44940,11 @@
       <c r="Q224" t="n">
         <v>0</v>
       </c>
+      <c r="S224" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA224" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -44667,13 +44957,23 @@
       </c>
       <c r="AP224" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR224" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS224" t="inlineStr"/>
       <c r="AT224" t="n">
         <v>0</v>
       </c>
+      <c r="AU224" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV224" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -45826,6 +46126,11 @@
       <c r="Q230" t="n">
         <v>0</v>
       </c>
+      <c r="S230" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA230" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -45838,13 +46143,23 @@
       </c>
       <c r="AP230" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR230" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS230" t="inlineStr"/>
       <c r="AT230" t="n">
         <v>0</v>
       </c>
+      <c r="AU230" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV230" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -46997,6 +47312,11 @@
       <c r="Q236" t="n">
         <v>0</v>
       </c>
+      <c r="S236" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA236" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -47009,13 +47329,23 @@
       </c>
       <c r="AP236" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR236" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS236" t="inlineStr"/>
       <c r="AT236" t="n">
         <v>0</v>
       </c>
+      <c r="AU236" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV236" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -48168,6 +48498,11 @@
       <c r="Q242" t="n">
         <v>0</v>
       </c>
+      <c r="S242" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA242" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -48180,13 +48515,23 @@
       </c>
       <c r="AP242" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR242" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS242" t="inlineStr"/>
       <c r="AT242" t="n">
         <v>0</v>
       </c>
+      <c r="AU242" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV242" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -49339,6 +49684,11 @@
       <c r="Q248" t="n">
         <v>0</v>
       </c>
+      <c r="S248" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA248" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -49351,13 +49701,23 @@
       </c>
       <c r="AP248" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR248" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS248" t="inlineStr"/>
       <c r="AT248" t="n">
         <v>0</v>
       </c>
+      <c r="AU248" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV248" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -55668,6 +56028,11 @@
       <c r="Q280" t="n">
         <v>0</v>
       </c>
+      <c r="S280" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA280" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -55680,13 +56045,23 @@
       </c>
       <c r="AP280" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR280" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS280" t="inlineStr"/>
       <c r="AT280" t="n">
         <v>0</v>
       </c>
+      <c r="AU280" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV280" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -63026,6 +63401,11 @@
       <c r="Q317" t="n">
         <v>0</v>
       </c>
+      <c r="S317" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA317" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -63038,13 +63418,23 @@
       </c>
       <c r="AP317" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR317" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS317" t="inlineStr"/>
       <c r="AT317" t="n">
         <v>0</v>
       </c>
+      <c r="AU317" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV317" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -64197,6 +64587,11 @@
       <c r="Q323" t="n">
         <v>0</v>
       </c>
+      <c r="S323" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA323" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -64209,13 +64604,23 @@
       </c>
       <c r="AP323" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR323" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS323" t="inlineStr"/>
       <c r="AT323" t="n">
         <v>0</v>
       </c>
+      <c r="AU323" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV323" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -65368,6 +65773,11 @@
       <c r="Q329" t="n">
         <v>0</v>
       </c>
+      <c r="S329" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA329" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -65380,13 +65790,23 @@
       </c>
       <c r="AP329" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR329" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS329" t="inlineStr"/>
       <c r="AT329" t="n">
         <v>0</v>
       </c>
+      <c r="AU329" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV329" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -66539,6 +66959,11 @@
       <c r="Q335" t="n">
         <v>0</v>
       </c>
+      <c r="S335" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA335" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -66551,13 +66976,23 @@
       </c>
       <c r="AP335" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR335" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS335" t="inlineStr"/>
       <c r="AT335" t="n">
         <v>0</v>
       </c>
+      <c r="AU335" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV335" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -67710,6 +68145,11 @@
       <c r="Q341" t="n">
         <v>0</v>
       </c>
+      <c r="S341" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA341" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -67722,13 +68162,23 @@
       </c>
       <c r="AP341" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR341" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS341" t="inlineStr"/>
       <c r="AT341" t="n">
         <v>0</v>
       </c>
+      <c r="AU341" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV341" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -68881,6 +69331,11 @@
       <c r="Q347" t="n">
         <v>0</v>
       </c>
+      <c r="S347" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA347" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -68893,13 +69348,23 @@
       </c>
       <c r="AP347" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR347" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS347" t="inlineStr"/>
       <c r="AT347" t="n">
         <v>0</v>
       </c>
+      <c r="AU347" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV347" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -70052,6 +70517,11 @@
       <c r="Q353" t="n">
         <v>0</v>
       </c>
+      <c r="S353" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA353" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -70064,13 +70534,23 @@
       </c>
       <c r="AP353" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR353" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS353" t="inlineStr"/>
       <c r="AT353" t="n">
         <v>0</v>
       </c>
+      <c r="AU353" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV353" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -71223,6 +71703,11 @@
       <c r="Q359" t="n">
         <v>0</v>
       </c>
+      <c r="S359" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA359" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -71235,13 +71720,23 @@
       </c>
       <c r="AP359" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR359" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS359" t="inlineStr"/>
       <c r="AT359" t="n">
         <v>0</v>
       </c>
+      <c r="AU359" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV359" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -72394,6 +72889,11 @@
       <c r="Q365" t="n">
         <v>0</v>
       </c>
+      <c r="S365" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA365" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -72406,13 +72906,23 @@
       </c>
       <c r="AP365" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR365" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS365" t="inlineStr"/>
       <c r="AT365" t="n">
         <v>0</v>
       </c>
+      <c r="AU365" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV365" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -73565,6 +74075,11 @@
       <c r="Q371" t="n">
         <v>0</v>
       </c>
+      <c r="S371" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA371" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -73577,13 +74092,23 @@
       </c>
       <c r="AP371" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR371" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS371" t="inlineStr"/>
       <c r="AT371" t="n">
         <v>0</v>
       </c>
+      <c r="AU371" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV371" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -74736,6 +75261,11 @@
       <c r="Q377" t="n">
         <v>0</v>
       </c>
+      <c r="S377" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA377" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -74748,12 +75278,22 @@
       </c>
       <c r="AP377" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR377" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS377" t="inlineStr"/>
       <c r="AT377" t="n">
         <v>0</v>
+      </c>
+      <c r="AU377" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV377" t="inlineStr">
         <is>
